--- a/static/files/lab_test_import_template.xlsx
+++ b/static/files/lab_test_import_template.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adeba\Desktop\clinic365\static\files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev3\clinic365\static\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="10">
   <si>
     <t>item</t>
   </si>
@@ -35,22 +35,25 @@
     <t>rate</t>
   </si>
   <si>
-    <t>ABC Test</t>
-  </si>
-  <si>
-    <t>Graham 3 kits</t>
-  </si>
-  <si>
-    <t>Malaria Parasites</t>
-  </si>
-  <si>
-    <t>ATMM10</t>
-  </si>
-  <si>
-    <t>GMMM11</t>
-  </si>
-  <si>
-    <t>MPMM12</t>
+    <t>plan</t>
+  </si>
+  <si>
+    <t>Single</t>
+  </si>
+  <si>
+    <t>Family</t>
+  </si>
+  <si>
+    <t>ANC</t>
+  </si>
+  <si>
+    <t>AIICO MULTISHIELD</t>
+  </si>
+  <si>
+    <t>MTC scan</t>
+  </si>
+  <si>
+    <t>MTC</t>
   </si>
 </sst>
 </file>
@@ -368,14 +371,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="15.1796875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.26953125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -385,38 +389,78 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2">
+        <v>800</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3">
+        <v>1000</v>
+      </c>
+      <c r="D3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4">
+        <v>1200</v>
+      </c>
+      <c r="D4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5">
+        <v>800</v>
+      </c>
+      <c r="D5" t="s">
         <v>6</v>
       </c>
-      <c r="C2">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6">
+        <v>7000</v>
+      </c>
+      <c r="D6" t="s">
         <v>7</v>
-      </c>
-      <c r="C3">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4">
-        <v>5000</v>
       </c>
     </row>
   </sheetData>
